--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H657"/>
+  <dimension ref="A1:H661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20146,6 +20146,126 @@
         <v>362.16</v>
       </c>
       <c r="H657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>352.49</v>
+      </c>
+      <c r="C658" t="n">
+        <v>345.47</v>
+      </c>
+      <c r="D658" t="n">
+        <v>363.28</v>
+      </c>
+      <c r="E658" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="F658" t="n">
+        <v>383.91</v>
+      </c>
+      <c r="G658" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="C659" t="n">
+        <v>344.78</v>
+      </c>
+      <c r="D659" t="n">
+        <v>362.45</v>
+      </c>
+      <c r="E659" t="n">
+        <v>370.93</v>
+      </c>
+      <c r="F659" t="n">
+        <v>383.37</v>
+      </c>
+      <c r="G659" t="n">
+        <v>361.24</v>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="C660" t="n">
+        <v>344.59</v>
+      </c>
+      <c r="D660" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="E660" t="n">
+        <v>370.05</v>
+      </c>
+      <c r="F660" t="n">
+        <v>382.42</v>
+      </c>
+      <c r="G660" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>352.07</v>
+      </c>
+      <c r="C661" t="n">
+        <v>344.78</v>
+      </c>
+      <c r="D661" t="n">
+        <v>361.23</v>
+      </c>
+      <c r="E661" t="n">
+        <v>369.64</v>
+      </c>
+      <c r="F661" t="n">
+        <v>382.38</v>
+      </c>
+      <c r="G661" t="n">
+        <v>360.23</v>
+      </c>
+      <c r="H661" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20162,7 +20282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B684"/>
+  <dimension ref="A1:B688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27005,6 +27125,46 @@
       </c>
       <c r="B684" t="n">
         <v>-0.79</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>-0.26</v>
       </c>
     </row>
   </sheetData>
@@ -27173,28 +27333,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06844215302163517</v>
+        <v>0.05654814636810321</v>
       </c>
       <c r="J2" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K2" t="n">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01087171625546346</v>
+        <v>0.007375615927256551</v>
       </c>
       <c r="M2" t="n">
-        <v>3.938668437838596</v>
+        <v>3.966206066079361</v>
       </c>
       <c r="N2" t="n">
-        <v>24.00788435733849</v>
+        <v>24.43406055579942</v>
       </c>
       <c r="O2" t="n">
-        <v>4.899784113339943</v>
+        <v>4.943082090740495</v>
       </c>
       <c r="P2" t="n">
-        <v>360.0870903970744</v>
+        <v>360.212308412636</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27251,28 +27411,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1368557242110008</v>
+        <v>0.1218226233141634</v>
       </c>
       <c r="J3" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K3" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02543275690934144</v>
+        <v>0.02009140182255986</v>
       </c>
       <c r="M3" t="n">
-        <v>5.347758848070584</v>
+        <v>5.376527904699947</v>
       </c>
       <c r="N3" t="n">
-        <v>40.37259144749105</v>
+        <v>41.03935203282922</v>
       </c>
       <c r="O3" t="n">
-        <v>6.353942984280788</v>
+        <v>6.406196377947621</v>
       </c>
       <c r="P3" t="n">
-        <v>353.6099794596861</v>
+        <v>353.768319957089</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27329,28 +27489,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2314806661982385</v>
+        <v>0.2217940880828389</v>
       </c>
       <c r="J4" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K4" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L4" t="n">
-        <v>0.101898101507276</v>
+        <v>0.09430026142438841</v>
       </c>
       <c r="M4" t="n">
-        <v>4.140909012499068</v>
+        <v>4.157457694902307</v>
       </c>
       <c r="N4" t="n">
-        <v>26.56631341249357</v>
+        <v>26.7880159593272</v>
       </c>
       <c r="O4" t="n">
-        <v>5.154251974098043</v>
+        <v>5.175714053087478</v>
       </c>
       <c r="P4" t="n">
-        <v>363.7928169668475</v>
+        <v>363.8948542122051</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27407,28 +27567,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1557794045686093</v>
+        <v>0.1495707932048122</v>
       </c>
       <c r="J5" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K5" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04761363380344918</v>
+        <v>0.04440159990373371</v>
       </c>
       <c r="M5" t="n">
-        <v>4.04457392631557</v>
+        <v>4.04567043325381</v>
       </c>
       <c r="N5" t="n">
-        <v>27.30512972029021</v>
+        <v>27.29855506391507</v>
       </c>
       <c r="O5" t="n">
-        <v>5.225431055931195</v>
+        <v>5.224801916237119</v>
       </c>
       <c r="P5" t="n">
-        <v>371.4876444667024</v>
+        <v>371.5530487206719</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27485,28 +27645,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2295343364373979</v>
+        <v>0.2257020196453489</v>
       </c>
       <c r="J6" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K6" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1788906227387925</v>
+        <v>0.1753547829489804</v>
       </c>
       <c r="M6" t="n">
-        <v>2.696437581420827</v>
+        <v>2.698889887058606</v>
       </c>
       <c r="N6" t="n">
-        <v>13.60351319053477</v>
+        <v>13.58281202544458</v>
       </c>
       <c r="O6" t="n">
-        <v>3.688294075929246</v>
+        <v>3.685486674164564</v>
       </c>
       <c r="P6" t="n">
-        <v>380.0053872817755</v>
+        <v>380.0457610282784</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27563,28 +27723,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1624472014660545</v>
+        <v>0.1581942447760304</v>
       </c>
       <c r="J7" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K7" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0534826822469483</v>
+        <v>0.05139596827455573</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0494674434903</v>
+        <v>4.042471151910542</v>
       </c>
       <c r="N7" t="n">
-        <v>26.27133700249238</v>
+        <v>26.18825399320937</v>
       </c>
       <c r="O7" t="n">
-        <v>5.125557238241749</v>
+        <v>5.117446042041808</v>
       </c>
       <c r="P7" t="n">
-        <v>359.9304956507612</v>
+        <v>359.9753005783194</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27622,7 +27782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H657"/>
+  <dimension ref="A1:H661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55215,6 +55375,174 @@
         </is>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-36.30975141834173,174.7948721686644</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-36.31047852176527,174.79481494768612</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-36.311193508835174,174.79504864591243</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-36.3118958579321,174.79524187466524</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-36.3125455164988,174.7955949090679</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>-36.31328532345189,174.79565713484772</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-36.30975145649073,174.79487083323158</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-36.310478793078616,174.79480727141043</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-36.31119417671671,174.7950394401601</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-36.31189709617774,174.79523423119596</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>-36.31254700097428,174.79558918222997</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>-36.31328693378011,174.79565169668584</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-36.30975170763802,174.79486204163203</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-36.31047886778801,174.79480515765334</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-36.311195182561086,174.79502557607495</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-36.3118986528287,174.7952246222628</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-36.31254961255086,174.79557910723676</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>-36.31329089766393,174.79563831044018</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-36.30975155186319,174.79486749464948</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-36.310478793078616,174.79480727141043</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-36.31119515842082,174.79502590881302</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-36.31189937808629,174.79522014537335</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-36.31254972251196,174.79557868302652</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>-36.31329006153231,174.7956411341015</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20266,6 +20266,96 @@
         <v>360.23</v>
       </c>
       <c r="H661" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="C662" t="n">
+        <v>345.54</v>
+      </c>
+      <c r="D662" t="n">
+        <v>361.97</v>
+      </c>
+      <c r="E662" t="n">
+        <v>369.53</v>
+      </c>
+      <c r="F662" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="G662" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>353.42</v>
+      </c>
+      <c r="C663" t="n">
+        <v>346.36</v>
+      </c>
+      <c r="D663" t="n">
+        <v>362</v>
+      </c>
+      <c r="E663" t="n">
+        <v>369.64</v>
+      </c>
+      <c r="F663" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="G663" t="n">
+        <v>361.37</v>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>354.57</v>
+      </c>
+      <c r="C664" t="n">
+        <v>346.71</v>
+      </c>
+      <c r="D664" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="E664" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="F664" t="n">
+        <v>383.41</v>
+      </c>
+      <c r="G664" t="n">
+        <v>361.15</v>
+      </c>
+      <c r="H664" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20282,7 +20372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B688"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27165,6 +27255,36 @@
       </c>
       <c r="B688" t="n">
         <v>-0.26</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -27333,28 +27453,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05654814636810321</v>
+        <v>0.04910482975154019</v>
       </c>
       <c r="J2" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="K2" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007375615927256551</v>
+        <v>0.005559818787545301</v>
       </c>
       <c r="M2" t="n">
-        <v>3.966206066079361</v>
+        <v>3.981099735253796</v>
       </c>
       <c r="N2" t="n">
-        <v>24.43406055579942</v>
+        <v>24.63030239709699</v>
       </c>
       <c r="O2" t="n">
-        <v>4.943082090740495</v>
+        <v>4.962892543375989</v>
       </c>
       <c r="P2" t="n">
-        <v>360.212308412636</v>
+        <v>360.290901670213</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27411,28 +27531,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1218226233141634</v>
+        <v>0.1120304591451216</v>
       </c>
       <c r="J3" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="K3" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02009140182255986</v>
+        <v>0.01700386539371457</v>
       </c>
       <c r="M3" t="n">
-        <v>5.376527904699947</v>
+        <v>5.392334086443405</v>
       </c>
       <c r="N3" t="n">
-        <v>41.03935203282922</v>
+        <v>41.37916666718471</v>
       </c>
       <c r="O3" t="n">
-        <v>6.406196377947621</v>
+        <v>6.432664041218437</v>
       </c>
       <c r="P3" t="n">
-        <v>353.768319957089</v>
+        <v>353.8717688475585</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27489,28 +27609,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2217940880828389</v>
+        <v>0.2147072615508699</v>
       </c>
       <c r="J4" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="K4" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09430026142438841</v>
+        <v>0.08890780227811013</v>
       </c>
       <c r="M4" t="n">
-        <v>4.157457694902307</v>
+        <v>4.16922404091571</v>
       </c>
       <c r="N4" t="n">
-        <v>26.7880159593272</v>
+        <v>26.94146916324279</v>
       </c>
       <c r="O4" t="n">
-        <v>5.175714053087478</v>
+        <v>5.190517234654249</v>
       </c>
       <c r="P4" t="n">
-        <v>363.8948542122051</v>
+        <v>363.969724470677</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27567,28 +27687,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1495707932048122</v>
+        <v>0.1440954966351043</v>
       </c>
       <c r="J5" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="K5" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04440159990373371</v>
+        <v>0.04151533207415703</v>
       </c>
       <c r="M5" t="n">
-        <v>4.04567043325381</v>
+        <v>4.050010301422212</v>
       </c>
       <c r="N5" t="n">
-        <v>27.29855506391507</v>
+        <v>27.33901272458058</v>
       </c>
       <c r="O5" t="n">
-        <v>5.224801916237119</v>
+        <v>5.228672176048196</v>
       </c>
       <c r="P5" t="n">
-        <v>371.5530487206719</v>
+        <v>371.6108946212495</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27645,28 +27765,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2257020196453489</v>
+        <v>0.2230137405260059</v>
       </c>
       <c r="J6" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="K6" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1753547829489804</v>
+        <v>0.1729741907719533</v>
       </c>
       <c r="M6" t="n">
-        <v>2.698889887058606</v>
+        <v>2.700008192511914</v>
       </c>
       <c r="N6" t="n">
-        <v>13.58281202544458</v>
+        <v>13.5614571515579</v>
       </c>
       <c r="O6" t="n">
-        <v>3.685486674164564</v>
+        <v>3.682588376612013</v>
       </c>
       <c r="P6" t="n">
-        <v>380.0457610282784</v>
+        <v>380.0741604833726</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27723,28 +27843,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1581942447760304</v>
+        <v>0.1552941544969446</v>
       </c>
       <c r="J7" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="K7" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05139596827455573</v>
+        <v>0.05002821806794755</v>
       </c>
       <c r="M7" t="n">
-        <v>4.042471151910542</v>
+        <v>4.036210224210618</v>
       </c>
       <c r="N7" t="n">
-        <v>26.18825399320937</v>
+        <v>26.11627570266204</v>
       </c>
       <c r="O7" t="n">
-        <v>5.117446042041808</v>
+        <v>5.110408565140564</v>
       </c>
       <c r="P7" t="n">
-        <v>359.9753005783194</v>
+        <v>360.0059385223783</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27782,7 +27902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55543,6 +55663,132 @@
         </is>
       </c>
     </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-36.3097514246999,174.79487194609226</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-36.310478494240684,174.79481572643874</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-36.311194562961134,174.79503411635145</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-36.31189957266757,174.79521894425665</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-36.312549007764765,174.79558144039316</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>-36.31328903959357,174.795644585243</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-36.309751122686386,174.79488251826876</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-36.31047817180965,174.7948248489692</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-36.31119453882087,174.79503444908948</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-36.31189937808629,174.79522014537335</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-36.31254691850342,174.79558950038765</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>-36.31328653119809,174.79565305622634</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-36.30975075708984,174.79489531616647</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-36.31047803418641,174.79482874273214</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-36.311194458353306,174.7950355582163</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-36.31189980262724,174.79521752475506</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-36.312546891013135,174.7955896064402</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>-36.31328721249074,174.7956507554655</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
